--- a/examples/data/results/y_maze/phd.xlsx
+++ b/examples/data/results/y_maze/phd.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Before" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="After" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="0_before" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="1_after" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -597,55 +597,55 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>1580.992721134815</v>
+        <v>1645.304228514195</v>
       </c>
       <c r="C4" t="n">
-        <v>112.9280515096297</v>
+        <v>2.896585458857951</v>
       </c>
       <c r="D4" t="n">
-        <v>184.7754976399256</v>
+        <v>2.556935486218891</v>
       </c>
       <c r="E4" t="n">
-        <v>46.15384615384615</v>
+        <v>75</v>
       </c>
       <c r="F4" t="n">
-        <v>140.1428571428571</v>
+        <v>130.8</v>
       </c>
       <c r="G4" t="n">
-        <v>52.14285714285715</v>
+        <v>48.66666666666666</v>
       </c>
       <c r="H4" t="n">
-        <v>144.8571428571429</v>
+        <v>135.2</v>
       </c>
       <c r="I4" t="n">
-        <v>49.42857142857143</v>
+        <v>46.13333333333333</v>
       </c>
       <c r="J4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K4" t="n">
         <v>6</v>
       </c>
       <c r="L4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M4" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="N4" t="n">
         <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -656,16 +656,16 @@
         <v>2</v>
       </c>
       <c r="B5" t="n">
-        <v>1753.54114479749</v>
+        <v>1450.524596895432</v>
       </c>
       <c r="C5" t="n">
-        <v>125.2529389141064</v>
+        <v>3.00976477829655</v>
       </c>
       <c r="D5" t="n">
-        <v>214.955030836811</v>
+        <v>2.61575531621873</v>
       </c>
       <c r="E5" t="n">
-        <v>33.33333333333334</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="F5" t="n">
         <v>63.5</v>
@@ -680,16 +680,16 @@
         <v>7.785714285714286</v>
       </c>
       <c r="J5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K5" t="n">
         <v>3</v>
       </c>
       <c r="L5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M5" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="N5" t="n">
         <v>2</v>
@@ -701,7 +701,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
         <v>2</v>
@@ -715,16 +715,16 @@
         <v>3</v>
       </c>
       <c r="B6" t="n">
-        <v>1794.493577349269</v>
+        <v>1760.198293199506</v>
       </c>
       <c r="C6" t="n">
-        <v>128.1781126678049</v>
+        <v>3.067639714878043</v>
       </c>
       <c r="D6" t="n">
-        <v>217.0476741590508</v>
+        <v>2.494820084062144</v>
       </c>
       <c r="E6" t="n">
-        <v>23.07692307692308</v>
+        <v>40.625</v>
       </c>
       <c r="F6" t="n">
         <v>78.07142857142857</v>
@@ -739,34 +739,34 @@
         <v>44.78571428571428</v>
       </c>
       <c r="J6" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="K6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L6" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="M6" t="n">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="N6" t="n">
         <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P6" t="n">
         <v>4</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R6" t="n">
         <v>2</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -774,16 +774,16 @@
         <v>4</v>
       </c>
       <c r="B7" t="n">
-        <v>2153.825014110591</v>
+        <v>2163.743852439485</v>
       </c>
       <c r="C7" t="n">
-        <v>153.8446438650422</v>
+        <v>3.694828164491388</v>
       </c>
       <c r="D7" t="n">
-        <v>256.3676431746734</v>
+        <v>3.096043508555712</v>
       </c>
       <c r="E7" t="n">
-        <v>43.24324324324324</v>
+        <v>60.71428571428572</v>
       </c>
       <c r="F7" t="n">
         <v>72.78571428571429</v>
@@ -798,34 +798,34 @@
         <v>39.92857142857143</v>
       </c>
       <c r="J7" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K7" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="L7" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="M7" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="N7" t="n">
         <v>4</v>
       </c>
       <c r="O7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P7" t="n">
         <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R7" t="n">
         <v>2</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -833,16 +833,16 @@
         <v>5</v>
       </c>
       <c r="B8" t="n">
-        <v>2498.772119994873</v>
+        <v>2561.062915806921</v>
       </c>
       <c r="C8" t="n">
-        <v>178.4837228567766</v>
+        <v>4.30576986600787</v>
       </c>
       <c r="D8" t="n">
-        <v>297.2207559943654</v>
+        <v>3.452162232071018</v>
       </c>
       <c r="E8" t="n">
-        <v>43.18181818181818</v>
+        <v>50</v>
       </c>
       <c r="F8" t="n">
         <v>125.8571428571429</v>
@@ -857,16 +857,16 @@
         <v>20.21428571428572</v>
       </c>
       <c r="J8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K8" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L8" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="M8" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="N8" t="n">
         <v>4</v>
@@ -892,16 +892,16 @@
         <v>6</v>
       </c>
       <c r="B9" t="n">
-        <v>1197.405561147655</v>
+        <v>1106.28012579776</v>
       </c>
       <c r="C9" t="n">
-        <v>85.52896865340389</v>
+        <v>2.1090004804152</v>
       </c>
       <c r="D9" t="n">
-        <v>145.5966212169154</v>
+        <v>1.74680055370432</v>
       </c>
       <c r="E9" t="n">
-        <v>21.42857142857143</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="F9" t="n">
         <v>20.71428571428572</v>
@@ -916,16 +916,16 @@
         <v>12.42857142857143</v>
       </c>
       <c r="J9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L9" t="n">
         <v>4</v>
       </c>
       <c r="M9" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N9" t="n">
         <v>1</v>
@@ -940,7 +940,7 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -951,46 +951,46 @@
         <v>7</v>
       </c>
       <c r="B10" t="n">
-        <v>1760.174393113186</v>
+        <v>1834.05712078207</v>
       </c>
       <c r="C10" t="n">
-        <v>125.7267423652276</v>
+        <v>3.177116952464584</v>
       </c>
       <c r="D10" t="n">
-        <v>205.9649133529283</v>
+        <v>2.644779355551225</v>
       </c>
       <c r="E10" t="n">
-        <v>48.48484848484848</v>
+        <v>61.53846153846154</v>
       </c>
       <c r="F10" t="n">
-        <v>151.5</v>
+        <v>141.4</v>
       </c>
       <c r="G10" t="n">
-        <v>50.92857142857143</v>
+        <v>47.53333333333333</v>
       </c>
       <c r="H10" t="n">
-        <v>136.3571428571429</v>
+        <v>127.2666666666667</v>
       </c>
       <c r="I10" t="n">
-        <v>39.71428571428572</v>
+        <v>37.06666666666667</v>
       </c>
       <c r="J10" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K10" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="L10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M10" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="N10" t="n">
         <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P10" t="n">
         <v>5</v>
@@ -999,10 +999,10 @@
         <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -1010,16 +1010,16 @@
         <v>8</v>
       </c>
       <c r="B11" t="n">
-        <v>1503.587570608049</v>
+        <v>1449.866112973307</v>
       </c>
       <c r="C11" t="n">
-        <v>107.3991121862892</v>
+        <v>2.658931533908321</v>
       </c>
       <c r="D11" t="n">
-        <v>180.263504568274</v>
+        <v>2.212189454901255</v>
       </c>
       <c r="E11" t="n">
-        <v>34.78260869565217</v>
+        <v>62.5</v>
       </c>
       <c r="F11" t="n">
         <v>49.21428571428572</v>
@@ -1034,34 +1034,34 @@
         <v>16.78571428571428</v>
       </c>
       <c r="J11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K11" t="n">
         <v>4</v>
       </c>
       <c r="L11" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="M11" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="N11" t="n">
         <v>1</v>
       </c>
       <c r="O11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R11" t="n">
         <v>1</v>
       </c>
       <c r="S11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1069,16 +1069,16 @@
         <v>9</v>
       </c>
       <c r="B12" t="n">
-        <v>2489.313669102701</v>
+        <v>2362.09125055868</v>
       </c>
       <c r="C12" t="n">
-        <v>177.8081192216215</v>
+        <v>4.406116483331356</v>
       </c>
       <c r="D12" t="n">
-        <v>301.1845706785036</v>
+        <v>3.594517895189647</v>
       </c>
       <c r="E12" t="n">
-        <v>33.92857142857143</v>
+        <v>48.57142857142857</v>
       </c>
       <c r="F12" t="n">
         <v>155.0714285714286</v>
@@ -1093,34 +1093,34 @@
         <v>43.85714285714285</v>
       </c>
       <c r="J12" t="n">
+        <v>12</v>
+      </c>
+      <c r="K12" t="n">
+        <v>9</v>
+      </c>
+      <c r="L12" t="n">
         <v>16</v>
       </c>
-      <c r="K12" t="n">
-        <v>14</v>
-      </c>
-      <c r="L12" t="n">
-        <v>28</v>
-      </c>
       <c r="M12" t="n">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="N12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1128,16 +1128,16 @@
         <v>10</v>
       </c>
       <c r="B13" t="n">
-        <v>4557.916688597275</v>
+        <v>4289.573525876337</v>
       </c>
       <c r="C13" t="n">
-        <v>325.5654777569483</v>
+        <v>7.615122701378312</v>
       </c>
       <c r="D13" t="n">
-        <v>566.5551401772187</v>
+        <v>7.196205233877691</v>
       </c>
       <c r="E13" t="n">
-        <v>48.14814814814815</v>
+        <v>68.96551724137932</v>
       </c>
       <c r="F13" t="n">
         <v>120.6428571428571</v>
@@ -1152,31 +1152,31 @@
         <v>38.71428571428572</v>
       </c>
       <c r="J13" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="K13" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="L13" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="M13" t="n">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="N13" t="n">
         <v>11</v>
       </c>
       <c r="O13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="R13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1187,16 +1187,16 @@
         <v>11</v>
       </c>
       <c r="B14" t="n">
-        <v>1609.513395345443</v>
+        <v>1454.591558157947</v>
       </c>
       <c r="C14" t="n">
-        <v>114.9652425246745</v>
+        <v>2.872525707553605</v>
       </c>
       <c r="D14" t="n">
-        <v>196.8064425911259</v>
+        <v>2.36457900649989</v>
       </c>
       <c r="E14" t="n">
-        <v>44.44444444444444</v>
+        <v>60</v>
       </c>
       <c r="F14" t="n">
         <v>120.6428571428571</v>
@@ -1211,22 +1211,22 @@
         <v>9.714285714285714</v>
       </c>
       <c r="J14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K14" t="n">
         <v>5</v>
       </c>
       <c r="L14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M14" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P14" t="n">
         <v>2</v>
@@ -1246,16 +1246,16 @@
         <v>12</v>
       </c>
       <c r="B15" t="n">
-        <v>2003.964081946185</v>
+        <v>1609.996664770889</v>
       </c>
       <c r="C15" t="n">
-        <v>143.1402915675846</v>
+        <v>3.153110121935554</v>
       </c>
       <c r="D15" t="n">
-        <v>255.0196189716222</v>
+        <v>2.801590378760299</v>
       </c>
       <c r="E15" t="n">
-        <v>24</v>
+        <v>42.10526315789474</v>
       </c>
       <c r="F15" t="n">
         <v>50.07142857142857</v>
@@ -1270,22 +1270,22 @@
         <v>19.5</v>
       </c>
       <c r="J15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K15" t="n">
+        <v>6</v>
+      </c>
+      <c r="L15" t="n">
         <v>7</v>
       </c>
-      <c r="L15" t="n">
-        <v>11</v>
-      </c>
       <c r="M15" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P15" t="n">
         <v>1</v>
@@ -1297,7 +1297,7 @@
         <v>1</v>
       </c>
       <c r="S15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -1305,58 +1305,58 @@
         <v>13</v>
       </c>
       <c r="B16" t="n">
-        <v>2099.038225254778</v>
+        <v>2158.085476047264</v>
       </c>
       <c r="C16" t="n">
-        <v>149.9313018039127</v>
+        <v>3.706926233008345</v>
       </c>
       <c r="D16" t="n">
-        <v>249.5172605340318</v>
+        <v>3.121461555318213</v>
       </c>
       <c r="E16" t="n">
-        <v>18.46153846153846</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="F16" t="n">
-        <v>99.92857142857143</v>
+        <v>93.26666666666667</v>
       </c>
       <c r="G16" t="n">
-        <v>72.78571428571429</v>
+        <v>67.93333333333334</v>
       </c>
       <c r="H16" t="n">
-        <v>121.2142857142857</v>
+        <v>113.1333333333333</v>
       </c>
       <c r="I16" t="n">
-        <v>83.92857142857143</v>
+        <v>78.33333333333333</v>
       </c>
       <c r="J16" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="K16" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="L16" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="M16" t="n">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="N16" t="n">
         <v>1</v>
       </c>
       <c r="O16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -1364,16 +1364,16 @@
         <v>14</v>
       </c>
       <c r="B17" t="n">
-        <v>1429.050661037385</v>
+        <v>1441.288010194313</v>
       </c>
       <c r="C17" t="n">
-        <v>102.0750472169561</v>
+        <v>2.541337843025711</v>
       </c>
       <c r="D17" t="n">
-        <v>172.131268427918</v>
+        <v>2.157023679763361</v>
       </c>
       <c r="E17" t="n">
-        <v>30.76923076923077</v>
+        <v>42.10526315789474</v>
       </c>
       <c r="F17" t="n">
         <v>201.2142857142857</v>
@@ -1388,16 +1388,16 @@
         <v>22.14285714285714</v>
       </c>
       <c r="J17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K17" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L17" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="M17" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="N17" t="n">
         <v>1</v>
@@ -1412,10 +1412,10 @@
         <v>3</v>
       </c>
       <c r="R17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1423,16 +1423,16 @@
         <v>15</v>
       </c>
       <c r="B18" t="n">
-        <v>1912.955291206533</v>
+        <v>1710.46036281145</v>
       </c>
       <c r="C18" t="n">
-        <v>136.6396636576095</v>
+        <v>3.389020933260975</v>
       </c>
       <c r="D18" t="n">
-        <v>235.2790672248942</v>
+        <v>2.863752786062723</v>
       </c>
       <c r="E18" t="n">
-        <v>33.33333333333334</v>
+        <v>63.63636363636363</v>
       </c>
       <c r="F18" t="n">
         <v>69.28571428571429</v>
@@ -1447,25 +1447,25 @@
         <v>28.5</v>
       </c>
       <c r="J18" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="K18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L18" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="M18" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q18" t="n">
         <v>1</v>
@@ -1474,7 +1474,7 @@
         <v>3</v>
       </c>
       <c r="S18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -1482,16 +1482,16 @@
         <v>16</v>
       </c>
       <c r="B19" t="n">
-        <v>1888.041424899681</v>
+        <v>1659.390894890051</v>
       </c>
       <c r="C19" t="n">
-        <v>134.8601017785486</v>
+        <v>3.607574316988319</v>
       </c>
       <c r="D19" t="n">
-        <v>234.9862377266234</v>
+        <v>3.17452877243394</v>
       </c>
       <c r="E19" t="n">
-        <v>37.5</v>
+        <v>65</v>
       </c>
       <c r="F19" t="n">
         <v>78.64285714285714</v>
@@ -1506,25 +1506,25 @@
         <v>24.92857142857143</v>
       </c>
       <c r="J19" t="n">
+        <v>7</v>
+      </c>
+      <c r="K19" t="n">
+        <v>7</v>
+      </c>
+      <c r="L19" t="n">
         <v>8</v>
       </c>
-      <c r="K19" t="n">
-        <v>8</v>
-      </c>
-      <c r="L19" t="n">
-        <v>10</v>
-      </c>
       <c r="M19" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="N19" t="n">
         <v>2</v>
       </c>
       <c r="O19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q19" t="n">
         <v>1</v>
@@ -1533,7 +1533,7 @@
         <v>1</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -1541,16 +1541,16 @@
         <v>17</v>
       </c>
       <c r="B20" t="n">
-        <v>1361.226918059357</v>
+        <v>1208.010212177882</v>
       </c>
       <c r="C20" t="n">
-        <v>97.23049414709696</v>
+        <v>2.45675881040652</v>
       </c>
       <c r="D20" t="n">
-        <v>163.7443407362429</v>
+        <v>2.046677643592637</v>
       </c>
       <c r="E20" t="n">
-        <v>45.45454545454545</v>
+        <v>85.71428571428571</v>
       </c>
       <c r="F20" t="n">
         <v>89</v>
@@ -1565,22 +1565,22 @@
         <v>7.071428571428571</v>
       </c>
       <c r="J20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M20" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P20" t="n">
         <v>2</v>
@@ -1589,10 +1589,10 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1600,16 +1600,16 @@
         <v>18</v>
       </c>
       <c r="B21" t="n">
-        <v>1952.923901522671</v>
+        <v>1726.17963693992</v>
       </c>
       <c r="C21" t="n">
-        <v>139.4945643944765</v>
+        <v>3.467558484633131</v>
       </c>
       <c r="D21" t="n">
-        <v>238.3868731877024</v>
+        <v>2.915015547809081</v>
       </c>
       <c r="E21" t="n">
-        <v>42.85714285714285</v>
+        <v>52.94117647058823</v>
       </c>
       <c r="F21" t="n">
         <v>153.2142857142857</v>
@@ -1624,22 +1624,22 @@
         <v>15.07142857142857</v>
       </c>
       <c r="J21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K21" t="n">
         <v>6</v>
       </c>
       <c r="L21" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="M21" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N21" t="n">
         <v>1</v>
       </c>
       <c r="O21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P21" t="n">
         <v>1</v>
@@ -1648,7 +1648,7 @@
         <v>2</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -1659,16 +1659,16 @@
         <v>19</v>
       </c>
       <c r="B22" t="n">
-        <v>1518.52434264712</v>
+        <v>1317.871166268833</v>
       </c>
       <c r="C22" t="n">
-        <v>108.4660244747943</v>
+        <v>2.736800362518363</v>
       </c>
       <c r="D22" t="n">
-        <v>185.2106672754293</v>
+        <v>2.356881129727534</v>
       </c>
       <c r="E22" t="n">
-        <v>42.85714285714285</v>
+        <v>72.72727272727273</v>
       </c>
       <c r="F22" t="n">
         <v>73.14285714285714</v>
@@ -1683,25 +1683,25 @@
         <v>9.928571428571429</v>
       </c>
       <c r="J22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L22" t="n">
         <v>5</v>
       </c>
       <c r="M22" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -1710,7 +1710,7 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -1718,16 +1718,16 @@
         <v>20</v>
       </c>
       <c r="B23" t="n">
-        <v>1884.996655251896</v>
+        <v>1916.318221608491</v>
       </c>
       <c r="C23" t="n">
-        <v>134.6426182322783</v>
+        <v>3.223284647674362</v>
       </c>
       <c r="D23" t="n">
-        <v>224.7032459918448</v>
+        <v>2.627695738428454</v>
       </c>
       <c r="E23" t="n">
-        <v>22.72727272727273</v>
+        <v>43.75</v>
       </c>
       <c r="F23" t="n">
         <v>125.4285714285714</v>
@@ -1745,25 +1745,25 @@
         <v>11</v>
       </c>
       <c r="K23" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L23" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="M23" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="N23" t="n">
         <v>2</v>
       </c>
       <c r="O23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P23" t="n">
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R23" t="n">
         <v>2</v>
@@ -1777,16 +1777,16 @@
         <v>21</v>
       </c>
       <c r="B24" t="n">
-        <v>2178.778219290811</v>
+        <v>2229.116720422329</v>
       </c>
       <c r="C24" t="n">
-        <v>155.6270156636294</v>
+        <v>3.64963851420399</v>
       </c>
       <c r="D24" t="n">
-        <v>259.8726818819968</v>
+        <v>3.155341972045524</v>
       </c>
       <c r="E24" t="n">
-        <v>40</v>
+        <v>46.42857142857143</v>
       </c>
       <c r="F24" t="n">
         <v>214.4285714285714</v>
@@ -1801,34 +1801,34 @@
         <v>37.85714285714285</v>
       </c>
       <c r="J24" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K24" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="L24" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="M24" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="N24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1836,16 +1836,16 @@
         <v>22</v>
       </c>
       <c r="B25" t="n">
-        <v>2148.754116764948</v>
+        <v>2291.087287552011</v>
       </c>
       <c r="C25" t="n">
-        <v>153.482436911782</v>
+        <v>3.769017329948558</v>
       </c>
       <c r="D25" t="n">
-        <v>256.1748568066181</v>
+        <v>3.067646556995387</v>
       </c>
       <c r="E25" t="n">
-        <v>32.55813953488372</v>
+        <v>54.54545454545455</v>
       </c>
       <c r="F25" t="n">
         <v>161.8571428571429</v>
@@ -1860,34 +1860,34 @@
         <v>32.57142857142857</v>
       </c>
       <c r="J25" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="K25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L25" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M25" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O25" t="n">
         <v>5</v>
       </c>
       <c r="P25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q25" t="n">
         <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
@@ -1895,16 +1895,16 @@
         <v>23</v>
       </c>
       <c r="B26" t="n">
-        <v>2267.683297131296</v>
+        <v>1845.242700687087</v>
       </c>
       <c r="C26" t="n">
-        <v>161.9773783665212</v>
+        <v>3.683005666018075</v>
       </c>
       <c r="D26" t="n">
-        <v>282.237920249216</v>
+        <v>3.276147463855888</v>
       </c>
       <c r="E26" t="n">
-        <v>34.61538461538461</v>
+        <v>68.42105263157895</v>
       </c>
       <c r="F26" t="n">
         <v>82.21428571428571</v>
@@ -1919,34 +1919,34 @@
         <v>36.28571428571428</v>
       </c>
       <c r="J26" t="n">
+        <v>6</v>
+      </c>
+      <c r="K26" t="n">
         <v>7</v>
       </c>
-      <c r="K26" t="n">
-        <v>10</v>
-      </c>
       <c r="L26" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="M26" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -1954,16 +1954,16 @@
         <v>24</v>
       </c>
       <c r="B27" t="n">
-        <v>3094.575096981268</v>
+        <v>3093.731718065845</v>
       </c>
       <c r="C27" t="n">
-        <v>221.0410783558048</v>
+        <v>5.292819713590315</v>
       </c>
       <c r="D27" t="n">
-        <v>378.1175215076451</v>
+        <v>4.605897640687937</v>
       </c>
       <c r="E27" t="n">
-        <v>28.35820895522388</v>
+        <v>45.65217391304348</v>
       </c>
       <c r="F27" t="n">
         <v>90.5</v>
@@ -1978,34 +1978,34 @@
         <v>83.92857142857143</v>
       </c>
       <c r="J27" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="K27" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="L27" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="M27" t="n">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="N27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O27" t="n">
         <v>6</v>
       </c>
       <c r="P27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28">
@@ -2013,16 +2013,16 @@
         <v>25</v>
       </c>
       <c r="B28" t="n">
-        <v>1763.327192811899</v>
+        <v>1402.470362106041</v>
       </c>
       <c r="C28" t="n">
-        <v>125.9519423437071</v>
+        <v>2.935898515242035</v>
       </c>
       <c r="D28" t="n">
-        <v>220.7995935179262</v>
+        <v>2.612561783056195</v>
       </c>
       <c r="E28" t="n">
-        <v>50</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="F28" t="n">
         <v>34.92857142857143</v>
@@ -2040,7 +2040,7 @@
         <v>3</v>
       </c>
       <c r="K28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L28" t="n">
         <v>5</v>
@@ -2072,16 +2072,16 @@
         <v>26</v>
       </c>
       <c r="B29" t="n">
-        <v>2918.240211091832</v>
+        <v>2467.300373833516</v>
       </c>
       <c r="C29" t="n">
-        <v>208.4457293637023</v>
+        <v>5.344306203094201</v>
       </c>
       <c r="D29" t="n">
-        <v>358.3779498487742</v>
+        <v>4.456841146732388</v>
       </c>
       <c r="E29" t="n">
-        <v>40.90909090909091</v>
+        <v>59.375</v>
       </c>
       <c r="F29" t="n">
         <v>137.7142857142857</v>
@@ -2096,22 +2096,22 @@
         <v>32.21428571428572</v>
       </c>
       <c r="J29" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K29" t="n">
+        <v>10</v>
+      </c>
+      <c r="L29" t="n">
         <v>12</v>
       </c>
-      <c r="L29" t="n">
-        <v>19</v>
-      </c>
       <c r="M29" t="n">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="N29" t="n">
         <v>2</v>
       </c>
       <c r="O29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P29" t="n">
         <v>4</v>
@@ -2120,10 +2120,10 @@
         <v>3</v>
       </c>
       <c r="R29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -2131,16 +2131,16 @@
         <v>27</v>
       </c>
       <c r="B30" t="n">
-        <v>2346.655997945926</v>
+        <v>2640.698326827673</v>
       </c>
       <c r="C30" t="n">
-        <v>167.6182855675661</v>
+        <v>4.057060867313717</v>
       </c>
       <c r="D30" t="n">
-        <v>277.8067425269393</v>
+        <v>3.284742300296879</v>
       </c>
       <c r="E30" t="n">
-        <v>28.07017543859649</v>
+        <v>51.21951219512195</v>
       </c>
       <c r="F30" t="n">
         <v>84.14285714285714</v>
@@ -2155,31 +2155,31 @@
         <v>48.64285714285715</v>
       </c>
       <c r="J30" t="n">
+        <v>12</v>
+      </c>
+      <c r="K30" t="n">
+        <v>13</v>
+      </c>
+      <c r="L30" t="n">
         <v>18</v>
       </c>
-      <c r="K30" t="n">
-        <v>14</v>
-      </c>
-      <c r="L30" t="n">
-        <v>27</v>
-      </c>
       <c r="M30" t="n">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="N30" t="n">
         <v>5</v>
       </c>
       <c r="O30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S30" t="n">
         <v>2</v>
@@ -2190,16 +2190,16 @@
         <v>28</v>
       </c>
       <c r="B31" t="n">
-        <v>2919.608213834435</v>
+        <v>2716.574992529363</v>
       </c>
       <c r="C31" t="n">
-        <v>208.5434438453168</v>
+        <v>5.268233684219781</v>
       </c>
       <c r="D31" t="n">
-        <v>353.2074988007202</v>
+        <v>4.451567477068865</v>
       </c>
       <c r="E31" t="n">
-        <v>25.75757575757576</v>
+        <v>43.47826086956522</v>
       </c>
       <c r="F31" t="n">
         <v>98.35714285714286</v>
@@ -2214,34 +2214,34 @@
         <v>62.92857142857143</v>
       </c>
       <c r="J31" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="K31" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="L31" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="M31" t="n">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="N31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O31" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P31" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q31" t="n">
         <v>2</v>
       </c>
       <c r="R31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -2249,16 +2249,16 @@
         <v>29</v>
       </c>
       <c r="B32" t="n">
-        <v>2177.959628010336</v>
+        <v>2021.84545092759</v>
       </c>
       <c r="C32" t="n">
-        <v>155.5685448578811</v>
+        <v>3.842655915755341</v>
       </c>
       <c r="D32" t="n">
-        <v>265.5114634989358</v>
+        <v>3.215951487293517</v>
       </c>
       <c r="E32" t="n">
-        <v>27.58620689655172</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="F32" t="n">
         <v>67.35714285714286</v>
@@ -2273,22 +2273,22 @@
         <v>177.7857142857143</v>
       </c>
       <c r="J32" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="K32" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L32" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="M32" t="n">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="N32" t="n">
         <v>2</v>
       </c>
       <c r="O32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P32" t="n">
         <v>4</v>
@@ -2297,7 +2297,7 @@
         <v>2</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -2308,16 +2308,16 @@
         <v>30</v>
       </c>
       <c r="B33" t="n">
-        <v>2041.904283896392</v>
+        <v>1823.249623286288</v>
       </c>
       <c r="C33" t="n">
-        <v>145.8503059925994</v>
+        <v>3.82899849632734</v>
       </c>
       <c r="D33" t="n">
-        <v>248.9080394572361</v>
+        <v>3.198915111906864</v>
       </c>
       <c r="E33" t="n">
-        <v>35.8974358974359</v>
+        <v>70.83333333333333</v>
       </c>
       <c r="F33" t="n">
         <v>168.6428571428571</v>
@@ -2335,31 +2335,31 @@
         <v>10</v>
       </c>
       <c r="K33" t="n">
+        <v>6</v>
+      </c>
+      <c r="L33" t="n">
         <v>10</v>
       </c>
-      <c r="L33" t="n">
-        <v>21</v>
-      </c>
       <c r="M33" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="N33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R33" t="n">
         <v>3</v>
       </c>
       <c r="S33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
@@ -2367,16 +2367,16 @@
         <v>31</v>
       </c>
       <c r="B34" t="n">
-        <v>2400.554421785828</v>
+        <v>2327.444627270446</v>
       </c>
       <c r="C34" t="n">
-        <v>171.468172984702</v>
+        <v>3.990894039527676</v>
       </c>
       <c r="D34" t="n">
-        <v>294.1198974517216</v>
+        <v>3.865065997613557</v>
       </c>
       <c r="E34" t="n">
-        <v>26.53061224489796</v>
+        <v>40</v>
       </c>
       <c r="F34" t="n">
         <v>104.7142857142857</v>
@@ -2391,16 +2391,16 @@
         <v>44.14285714285715</v>
       </c>
       <c r="J34" t="n">
+        <v>12</v>
+      </c>
+      <c r="K34" t="n">
+        <v>8</v>
+      </c>
+      <c r="L34" t="n">
         <v>17</v>
       </c>
-      <c r="K34" t="n">
-        <v>9</v>
-      </c>
-      <c r="L34" t="n">
-        <v>25</v>
-      </c>
       <c r="M34" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="N34" t="n">
         <v>2</v>
@@ -2415,10 +2415,10 @@
         <v>3</v>
       </c>
       <c r="R34" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2426,40 +2426,40 @@
         <v>32</v>
       </c>
       <c r="B35" t="n">
-        <v>1693.092423241385</v>
+        <v>1688.24315891791</v>
       </c>
       <c r="C35" t="n">
-        <v>120.9351730886704</v>
+        <v>2.934051183621572</v>
       </c>
       <c r="D35" t="n">
-        <v>200.3368693734568</v>
+        <v>2.426572565876521</v>
       </c>
       <c r="E35" t="n">
-        <v>38.23529411764706</v>
+        <v>62.5</v>
       </c>
       <c r="F35" t="n">
-        <v>128.2142857142857</v>
+        <v>129.4285714285714</v>
       </c>
       <c r="G35" t="n">
-        <v>110.5</v>
+        <v>110.2142857142857</v>
       </c>
       <c r="H35" t="n">
         <v>95.35714285714286</v>
       </c>
       <c r="I35" t="n">
-        <v>48.71428571428572</v>
+        <v>49.07142857142857</v>
       </c>
       <c r="J35" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K35" t="n">
         <v>8</v>
       </c>
       <c r="L35" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="M35" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="N35" t="n">
         <v>4</v>
@@ -2471,10 +2471,10 @@
         <v>2</v>
       </c>
       <c r="Q35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S35" t="n">
         <v>2</v>
@@ -2485,16 +2485,16 @@
         <v>33</v>
       </c>
       <c r="B36" t="n">
-        <v>1713.899104455521</v>
+        <v>1641.082683488451</v>
       </c>
       <c r="C36" t="n">
-        <v>122.4213646039658</v>
+        <v>2.937198949861087</v>
       </c>
       <c r="D36" t="n">
-        <v>207.331410097522</v>
+        <v>2.579290659618904</v>
       </c>
       <c r="E36" t="n">
-        <v>32.14285714285715</v>
+        <v>50</v>
       </c>
       <c r="F36" t="n">
         <v>147.6428571428571</v>
@@ -2509,25 +2509,25 @@
         <v>38.35714285714285</v>
       </c>
       <c r="J36" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="K36" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L36" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="M36" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q36" t="n">
         <v>2</v>
@@ -2536,7 +2536,7 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2544,16 +2544,16 @@
         <v>34</v>
       </c>
       <c r="B37" t="n">
-        <v>2112.013679838192</v>
+        <v>1970.037614784859</v>
       </c>
       <c r="C37" t="n">
-        <v>150.8581199884423</v>
+        <v>3.743197942874466</v>
       </c>
       <c r="D37" t="n">
-        <v>250.7231680581978</v>
+        <v>3.118584151901926</v>
       </c>
       <c r="E37" t="n">
-        <v>22.95081967213115</v>
+        <v>38.88888888888889</v>
       </c>
       <c r="F37" t="n">
         <v>74.71428571428571</v>
@@ -2568,22 +2568,22 @@
         <v>168.7857142857143</v>
       </c>
       <c r="J37" t="n">
+        <v>11</v>
+      </c>
+      <c r="K37" t="n">
+        <v>13</v>
+      </c>
+      <c r="L37" t="n">
         <v>14</v>
       </c>
-      <c r="K37" t="n">
-        <v>24</v>
-      </c>
-      <c r="L37" t="n">
-        <v>25</v>
-      </c>
       <c r="M37" t="n">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P37" t="n">
         <v>4</v>
@@ -2592,10 +2592,10 @@
         <v>3</v>
       </c>
       <c r="R37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2603,16 +2603,16 @@
         <v>35</v>
       </c>
       <c r="B38" t="n">
-        <v>6215.459733811145</v>
+        <v>8660.044227823404</v>
       </c>
       <c r="C38" t="n">
-        <v>443.9614095579389</v>
+        <v>12.47802899248264</v>
       </c>
       <c r="D38" t="n">
-        <v>715.4187150569616</v>
+        <v>10.11827057437168</v>
       </c>
       <c r="E38" t="n">
-        <v>50.31055900621118</v>
+        <v>51.38888888888889</v>
       </c>
       <c r="F38" t="n">
         <v>101.2142857142857</v>
@@ -2627,28 +2627,28 @@
         <v>29.92857142857143</v>
       </c>
       <c r="J38" t="n">
+        <v>46</v>
+      </c>
+      <c r="K38" t="n">
         <v>52</v>
       </c>
-      <c r="K38" t="n">
-        <v>57</v>
-      </c>
       <c r="L38" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="M38" t="n">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="N38" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O38" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="P38" t="n">
         <v>20</v>
       </c>
       <c r="Q38" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="R38" t="n">
         <v>9</v>
@@ -2662,16 +2662,16 @@
         <v>36</v>
       </c>
       <c r="B39" t="n">
-        <v>2509.555603569918</v>
+        <v>2758.196017409713</v>
       </c>
       <c r="C39" t="n">
-        <v>179.2539716835656</v>
+        <v>4.353082746598112</v>
       </c>
       <c r="D39" t="n">
-        <v>297.8009207687883</v>
+        <v>3.727360011855846</v>
       </c>
       <c r="E39" t="n">
-        <v>34.54545454545455</v>
+        <v>55</v>
       </c>
       <c r="F39" t="n">
         <v>133.5</v>
@@ -2686,25 +2686,25 @@
         <v>40.35714285714285</v>
       </c>
       <c r="J39" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="K39" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L39" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="M39" t="n">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="N39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O39" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P39" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -2713,7 +2713,7 @@
         <v>2</v>
       </c>
       <c r="S39" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40">
@@ -2721,16 +2721,16 @@
         <v>37</v>
       </c>
       <c r="B40" t="n">
-        <v>1772.167737864203</v>
+        <v>1913.651246267495</v>
       </c>
       <c r="C40" t="n">
-        <v>126.583409847443</v>
+        <v>2.957687039352884</v>
       </c>
       <c r="D40" t="n">
-        <v>213.4712303533968</v>
+        <v>2.459230888634713</v>
       </c>
       <c r="E40" t="n">
-        <v>39.53488372093023</v>
+        <v>59.25925925925926</v>
       </c>
       <c r="F40" t="n">
         <v>211.4285714285714</v>
@@ -2745,34 +2745,34 @@
         <v>39.78571428571428</v>
       </c>
       <c r="J40" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="K40" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L40" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M40" t="n">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="N40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q40" t="n">
         <v>3</v>
       </c>
       <c r="R40" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2780,16 +2780,16 @@
         <v>38</v>
       </c>
       <c r="B41" t="n">
-        <v>2767.517031063991</v>
+        <v>2524.998180654878</v>
       </c>
       <c r="C41" t="n">
-        <v>197.6797879331422</v>
+        <v>4.822139013535772</v>
       </c>
       <c r="D41" t="n">
-        <v>340.9655012090435</v>
+        <v>4.297178526698123</v>
       </c>
       <c r="E41" t="n">
-        <v>44.73684210526316</v>
+        <v>40.625</v>
       </c>
       <c r="F41" t="n">
         <v>160.7142857142857</v>
@@ -2804,34 +2804,34 @@
         <v>38</v>
       </c>
       <c r="J41" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K41" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L41" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="M41" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P41" t="n">
         <v>2</v>
       </c>
       <c r="Q41" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2839,16 +2839,16 @@
         <v>39</v>
       </c>
       <c r="B42" t="n">
-        <v>2279.105709188381</v>
+        <v>2010.868035177944</v>
       </c>
       <c r="C42" t="n">
-        <v>162.7932649420272</v>
+        <v>3.844817303859919</v>
       </c>
       <c r="D42" t="n">
-        <v>283.6588224402965</v>
+        <v>3.55853436093765</v>
       </c>
       <c r="E42" t="n">
-        <v>40</v>
+        <v>54.16666666666666</v>
       </c>
       <c r="F42" t="n">
         <v>269.0714285714286</v>
@@ -2863,16 +2863,16 @@
         <v>20.42857142857143</v>
       </c>
       <c r="J42" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="K42" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L42" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M42" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="N42" t="n">
         <v>3</v>
@@ -2884,7 +2884,7 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R42" t="n">
         <v>1</v>
@@ -2898,16 +2898,16 @@
         <v>40</v>
       </c>
       <c r="B43" t="n">
-        <v>2126.856035924899</v>
+        <v>1669.513928134365</v>
       </c>
       <c r="C43" t="n">
-        <v>151.9182882803499</v>
+        <v>3.72173984301002</v>
       </c>
       <c r="D43" t="n">
-        <v>261.7072292066644</v>
+        <v>3.158477616855822</v>
       </c>
       <c r="E43" t="n">
-        <v>28.57142857142857</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="F43" t="n">
         <v>311.2857142857143</v>
@@ -2925,28 +2925,28 @@
         <v>4</v>
       </c>
       <c r="K43" t="n">
+        <v>2</v>
+      </c>
+      <c r="L43" t="n">
         <v>5</v>
       </c>
-      <c r="L43" t="n">
-        <v>7</v>
-      </c>
       <c r="M43" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P43" t="n">
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -2957,16 +2957,16 @@
         <v>41</v>
       </c>
       <c r="B44" t="n">
-        <v>1901.774507703429</v>
+        <v>1940.654564460158</v>
       </c>
       <c r="C44" t="n">
-        <v>135.8410362645306</v>
+        <v>3.456159871426938</v>
       </c>
       <c r="D44" t="n">
-        <v>228.2456059007326</v>
+        <v>2.775428870859179</v>
       </c>
       <c r="E44" t="n">
-        <v>34.09090909090909</v>
+        <v>51.51515151515152</v>
       </c>
       <c r="F44" t="n">
         <v>196.5714285714286</v>
@@ -2981,16 +2981,16 @@
         <v>18.28571428571428</v>
       </c>
       <c r="J44" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="K44" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="L44" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M44" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="N44" t="n">
         <v>2</v>
@@ -2999,16 +2999,16 @@
         <v>3</v>
       </c>
       <c r="P44" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q44" t="n">
         <v>1</v>
       </c>
       <c r="R44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S44" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45">
@@ -3016,16 +3016,16 @@
         <v>42</v>
       </c>
       <c r="B45" t="n">
-        <v>1617.855250075084</v>
+        <v>1671.200219974667</v>
       </c>
       <c r="C45" t="n">
-        <v>115.5610892910775</v>
+        <v>2.874776117809501</v>
       </c>
       <c r="D45" t="n">
-        <v>191.9565782469196</v>
+        <v>2.398026224161369</v>
       </c>
       <c r="E45" t="n">
-        <v>41.1764705882353</v>
+        <v>42.30769230769231</v>
       </c>
       <c r="F45" t="n">
         <v>237.2142857142857</v>
@@ -3040,22 +3040,22 @@
         <v>22.35714285714286</v>
       </c>
       <c r="J45" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K45" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L45" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M45" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="N45" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P45" t="n">
         <v>0</v>
@@ -3064,7 +3064,7 @@
         <v>3</v>
       </c>
       <c r="R45" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -3075,16 +3075,16 @@
         <v>43</v>
       </c>
       <c r="B46" t="n">
-        <v>2974.996492775066</v>
+        <v>3190.991189873655</v>
       </c>
       <c r="C46" t="n">
-        <v>212.4997494839332</v>
+        <v>5.318379838173833</v>
       </c>
       <c r="D46" t="n">
-        <v>351.3261065220397</v>
+        <v>4.457290980847888</v>
       </c>
       <c r="E46" t="n">
-        <v>29.62962962962963</v>
+        <v>36.66666666666666</v>
       </c>
       <c r="F46" t="n">
         <v>114.3571428571429</v>
@@ -3099,25 +3099,25 @@
         <v>51.35714285714285</v>
       </c>
       <c r="J46" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="K46" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="L46" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="M46" t="n">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="N46" t="n">
         <v>5</v>
       </c>
       <c r="O46" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q46" t="n">
         <v>6</v>
@@ -3126,7 +3126,7 @@
         <v>5</v>
       </c>
       <c r="S46" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3134,16 +3134,16 @@
         <v>44</v>
       </c>
       <c r="B47" t="n">
-        <v>2371.2140659994</v>
+        <v>2468.676942985309</v>
       </c>
       <c r="C47" t="n">
-        <v>169.3724332856714</v>
+        <v>4.25264364225023</v>
       </c>
       <c r="D47" t="n">
-        <v>286.1287777749091</v>
+        <v>3.488790140102175</v>
       </c>
       <c r="E47" t="n">
-        <v>34</v>
+        <v>52.63157894736842</v>
       </c>
       <c r="F47" t="n">
         <v>221</v>
@@ -3158,34 +3158,34 @@
         <v>32.78571428571428</v>
       </c>
       <c r="J47" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K47" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="L47" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="M47" t="n">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="N47" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O47" t="n">
         <v>3</v>
       </c>
       <c r="P47" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R47" t="n">
         <v>2</v>
       </c>
       <c r="S47" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48">
@@ -3193,16 +3193,16 @@
         <v>45</v>
       </c>
       <c r="B48" t="n">
-        <v>3142.405526092095</v>
+        <v>3036.927405869823</v>
       </c>
       <c r="C48" t="n">
-        <v>224.4575375780068</v>
+        <v>5.887688994134234</v>
       </c>
       <c r="D48" t="n">
-        <v>382.5967832545477</v>
+        <v>4.860418070616424</v>
       </c>
       <c r="E48" t="n">
-        <v>28.98550724637681</v>
+        <v>46</v>
       </c>
       <c r="F48" t="n">
         <v>82.35714285714286</v>
@@ -3217,31 +3217,31 @@
         <v>37.71428571428572</v>
       </c>
       <c r="J48" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="K48" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="L48" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="M48" t="n">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="N48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O48" t="n">
         <v>5</v>
       </c>
       <c r="P48" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q48" t="n">
         <v>5</v>
       </c>
       <c r="R48" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S48" t="n">
         <v>2</v>
@@ -3252,16 +3252,16 @@
         <v>46</v>
       </c>
       <c r="B49" t="n">
-        <v>2439.120377988182</v>
+        <v>2527.869250063786</v>
       </c>
       <c r="C49" t="n">
-        <v>174.222884142013</v>
+        <v>4.368879148466732</v>
       </c>
       <c r="D49" t="n">
-        <v>295.821772578673</v>
+        <v>3.541993646807029</v>
       </c>
       <c r="E49" t="n">
-        <v>46.93877551020408</v>
+        <v>57.14285714285715</v>
       </c>
       <c r="F49" t="n">
         <v>156.0714285714286</v>
@@ -3276,31 +3276,31 @@
         <v>68.92857142857143</v>
       </c>
       <c r="J49" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="K49" t="n">
         <v>13</v>
       </c>
       <c r="L49" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="M49" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="N49" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O49" t="n">
         <v>2</v>
       </c>
       <c r="P49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q49" t="n">
         <v>7</v>
       </c>
       <c r="R49" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -3464,55 +3464,55 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>1809.029075661907</v>
+        <v>1452.219090832688</v>
       </c>
       <c r="C4" t="n">
-        <v>129.2163625472791</v>
+        <v>3.79580831307616</v>
       </c>
       <c r="D4" t="n">
-        <v>223.7704805230963</v>
+        <v>2.931058008279591</v>
       </c>
       <c r="E4" t="n">
-        <v>20.68965517241379</v>
+        <v>38.09523809523809</v>
       </c>
       <c r="F4" t="n">
-        <v>98.42857142857143</v>
+        <v>114.8333333333333</v>
       </c>
       <c r="G4" t="n">
-        <v>53.42857142857143</v>
+        <v>62.33333333333334</v>
       </c>
       <c r="H4" t="n">
-        <v>119.7857142857143</v>
+        <v>139.75</v>
       </c>
       <c r="I4" t="n">
-        <v>39.42857142857143</v>
+        <v>46</v>
       </c>
       <c r="J4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="M4" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
         <v>2</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -3523,46 +3523,46 @@
         <v>2</v>
       </c>
       <c r="B5" t="n">
-        <v>2262.176412336398</v>
+        <v>1952.320307521677</v>
       </c>
       <c r="C5" t="n">
-        <v>161.5840294525999</v>
+        <v>4.536757941299255</v>
       </c>
       <c r="D5" t="n">
-        <v>280.3115838227657</v>
+        <v>3.471960585448513</v>
       </c>
       <c r="E5" t="n">
-        <v>41.86046511627907</v>
+        <v>58.06451612903226</v>
       </c>
       <c r="F5" t="n">
-        <v>96.85714285714286</v>
+        <v>113</v>
       </c>
       <c r="G5" t="n">
-        <v>66.64285714285714</v>
+        <v>77.75</v>
       </c>
       <c r="H5" t="n">
-        <v>137.7857142857143</v>
+        <v>160.75</v>
       </c>
       <c r="I5" t="n">
-        <v>30.42857142857143</v>
+        <v>35.5</v>
       </c>
       <c r="J5" t="n">
+        <v>10</v>
+      </c>
+      <c r="K5" t="n">
+        <v>10</v>
+      </c>
+      <c r="L5" t="n">
         <v>13</v>
       </c>
-      <c r="K5" t="n">
-        <v>14</v>
-      </c>
-      <c r="L5" t="n">
-        <v>18</v>
-      </c>
       <c r="M5" t="n">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="N5" t="n">
         <v>3</v>
       </c>
       <c r="O5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
@@ -3574,7 +3574,7 @@
         <v>3</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -3582,58 +3582,58 @@
         <v>3</v>
       </c>
       <c r="B6" t="n">
-        <v>2501.270335233242</v>
+        <v>1927.772671963392</v>
       </c>
       <c r="C6" t="n">
-        <v>178.6621668023745</v>
+        <v>5.032236206674624</v>
       </c>
       <c r="D6" t="n">
-        <v>313.3173363214231</v>
+        <v>3.823731000344875</v>
       </c>
       <c r="E6" t="n">
-        <v>29.41176470588235</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="F6" t="n">
-        <v>94.21428571428571</v>
+        <v>109.9166666666667</v>
       </c>
       <c r="G6" t="n">
-        <v>72.21428571428571</v>
+        <v>84.25</v>
       </c>
       <c r="H6" t="n">
-        <v>86.42857142857143</v>
+        <v>100.8333333333333</v>
       </c>
       <c r="I6" t="n">
-        <v>63.21428571428572</v>
+        <v>73.75</v>
       </c>
       <c r="J6" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="K6" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="L6" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="M6" t="n">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="N6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q6" t="n">
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -3641,58 +3641,58 @@
         <v>4</v>
       </c>
       <c r="B7" t="n">
-        <v>2902.389971405166</v>
+        <v>2365.293124209453</v>
       </c>
       <c r="C7" t="n">
-        <v>207.3135693860833</v>
+        <v>6.029282324352768</v>
       </c>
       <c r="D7" t="n">
-        <v>360.5977671836231</v>
+        <v>4.505272742021941</v>
       </c>
       <c r="E7" t="n">
-        <v>22.44897959183674</v>
+        <v>31.42857142857143</v>
       </c>
       <c r="F7" t="n">
-        <v>100.7142857142857</v>
+        <v>117.5</v>
       </c>
       <c r="G7" t="n">
-        <v>77.5</v>
+        <v>90.41666666666667</v>
       </c>
       <c r="H7" t="n">
-        <v>98.71428571428571</v>
+        <v>115.1666666666667</v>
       </c>
       <c r="I7" t="n">
-        <v>38.85714285714285</v>
+        <v>45.33333333333334</v>
       </c>
       <c r="J7" t="n">
+        <v>11</v>
+      </c>
+      <c r="K7" t="n">
+        <v>14</v>
+      </c>
+      <c r="L7" t="n">
         <v>12</v>
       </c>
-      <c r="K7" t="n">
-        <v>23</v>
-      </c>
-      <c r="L7" t="n">
-        <v>16</v>
-      </c>
       <c r="M7" t="n">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O7" t="n">
         <v>2</v>
       </c>
       <c r="P7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -3700,55 +3700,55 @@
         <v>5</v>
       </c>
       <c r="B8" t="n">
-        <v>2758.051774334426</v>
+        <v>2375.45163142235</v>
       </c>
       <c r="C8" t="n">
-        <v>197.0036981667447</v>
+        <v>5.61827642685745</v>
       </c>
       <c r="D8" t="n">
-        <v>340.8025373397293</v>
+        <v>4.314649983706341</v>
       </c>
       <c r="E8" t="n">
-        <v>35.41666666666666</v>
+        <v>60.60606060606061</v>
       </c>
       <c r="F8" t="n">
-        <v>74.71428571428571</v>
+        <v>87.16666666666667</v>
       </c>
       <c r="G8" t="n">
-        <v>120.8571428571429</v>
+        <v>141</v>
       </c>
       <c r="H8" t="n">
-        <v>86.14285714285714</v>
+        <v>100.5</v>
       </c>
       <c r="I8" t="n">
-        <v>38.35714285714285</v>
+        <v>44.75</v>
       </c>
       <c r="J8" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="K8" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="L8" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="M8" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="N8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
@@ -3759,49 +3759,49 @@
         <v>6</v>
       </c>
       <c r="B9" t="n">
-        <v>1656.797762185033</v>
+        <v>1149.184943242805</v>
       </c>
       <c r="C9" t="n">
-        <v>118.3426972989309</v>
+        <v>3.570455273605019</v>
       </c>
       <c r="D9" t="n">
-        <v>209.1361322561646</v>
+        <v>2.537135225630052</v>
       </c>
       <c r="E9" t="n">
-        <v>66.66666666666667</v>
+        <v>80</v>
       </c>
       <c r="F9" t="n">
-        <v>16.71428571428572</v>
+        <v>23.4</v>
       </c>
       <c r="G9" t="n">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="H9" t="n">
-        <v>161.7142857142857</v>
+        <v>226.4</v>
       </c>
       <c r="I9" t="n">
-        <v>7.714285714285714</v>
+        <v>10.8</v>
       </c>
       <c r="J9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L9" t="n">
         <v>4</v>
       </c>
       <c r="M9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q9" t="n">
         <v>1</v>
@@ -3810,7 +3810,7 @@
         <v>2</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -3818,58 +3818,58 @@
         <v>7</v>
       </c>
       <c r="B10" t="n">
-        <v>2798.087445308052</v>
+        <v>2078.167697754865</v>
       </c>
       <c r="C10" t="n">
-        <v>199.8633889505751</v>
+        <v>5.893238630913486</v>
       </c>
       <c r="D10" t="n">
-        <v>348.699563226688</v>
+        <v>4.581028988862366</v>
       </c>
       <c r="E10" t="n">
-        <v>20.40816326530612</v>
+        <v>41.37931034482759</v>
       </c>
       <c r="F10" t="n">
-        <v>101.3571428571429</v>
+        <v>141.9</v>
       </c>
       <c r="G10" t="n">
-        <v>69.07142857142857</v>
+        <v>96.7</v>
       </c>
       <c r="H10" t="n">
-        <v>44.35714285714285</v>
+        <v>62.1</v>
       </c>
       <c r="I10" t="n">
-        <v>36.92857142857143</v>
+        <v>51.7</v>
       </c>
       <c r="J10" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="K10" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="L10" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="M10" t="n">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="N10" t="n">
         <v>2</v>
       </c>
       <c r="O10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -3877,16 +3877,16 @@
         <v>8</v>
       </c>
       <c r="B11" t="n">
-        <v>2064.184657203984</v>
+        <v>2174.108129408813</v>
       </c>
       <c r="C11" t="n">
-        <v>147.441761228856</v>
+        <v>3.669651123497846</v>
       </c>
       <c r="D11" t="n">
-        <v>240.6313827211673</v>
+        <v>3.095982832054532</v>
       </c>
       <c r="E11" t="n">
-        <v>23.52941176470588</v>
+        <v>51.72413793103448</v>
       </c>
       <c r="F11" t="n">
         <v>150.2857142857143</v>
@@ -3901,22 +3901,22 @@
         <v>33.07142857142857</v>
       </c>
       <c r="J11" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="K11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L11" t="n">
         <v>11</v>
       </c>
-      <c r="L11" t="n">
-        <v>21</v>
-      </c>
       <c r="M11" t="n">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="N11" t="n">
         <v>1</v>
       </c>
       <c r="O11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P11" t="n">
         <v>4</v>
@@ -3925,7 +3925,7 @@
         <v>2</v>
       </c>
       <c r="R11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S11" t="n">
         <v>3</v>
@@ -3936,16 +3936,16 @@
         <v>9</v>
       </c>
       <c r="B12" t="n">
-        <v>2485.477988507789</v>
+        <v>2570.341825896292</v>
       </c>
       <c r="C12" t="n">
-        <v>177.5341420362706</v>
+        <v>4.413247388324705</v>
       </c>
       <c r="D12" t="n">
-        <v>296.3331071209798</v>
+        <v>3.838715134489727</v>
       </c>
       <c r="E12" t="n">
-        <v>25</v>
+        <v>64.51612903225806</v>
       </c>
       <c r="F12" t="n">
         <v>170.8571428571429</v>
@@ -3960,34 +3960,34 @@
         <v>40.14285714285715</v>
       </c>
       <c r="J12" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="K12" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="L12" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="M12" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="N12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -3995,16 +3995,16 @@
         <v>10</v>
       </c>
       <c r="B13" t="n">
-        <v>3800.482818719197</v>
+        <v>3945.335091350283</v>
       </c>
       <c r="C13" t="n">
-        <v>271.4630584799427</v>
+        <v>6.410487339839162</v>
       </c>
       <c r="D13" t="n">
-        <v>455.8023199399825</v>
+        <v>5.284032309794831</v>
       </c>
       <c r="E13" t="n">
-        <v>28.28282828282828</v>
+        <v>55.93220338983051</v>
       </c>
       <c r="F13" t="n">
         <v>81</v>
@@ -4019,31 +4019,31 @@
         <v>59.28571428571428</v>
       </c>
       <c r="J13" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="K13" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="L13" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="M13" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="N13" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
         <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R13" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -4054,58 +4054,58 @@
         <v>11</v>
       </c>
       <c r="B14" t="n">
-        <v>2720.87607451326</v>
+        <v>2370.399543666033</v>
       </c>
       <c r="C14" t="n">
-        <v>194.3482910366614</v>
+        <v>4.677448056670533</v>
       </c>
       <c r="D14" t="n">
-        <v>334.6390315249488</v>
+        <v>4.351338497555239</v>
       </c>
       <c r="E14" t="n">
-        <v>31.70731707317073</v>
+        <v>37.03703703703704</v>
       </c>
       <c r="F14" t="n">
-        <v>87.35714285714286</v>
+        <v>81.53333333333333</v>
       </c>
       <c r="G14" t="n">
-        <v>95.42857142857143</v>
+        <v>89.06666666666666</v>
       </c>
       <c r="H14" t="n">
-        <v>169.1428571428571</v>
+        <v>157.8666666666667</v>
       </c>
       <c r="I14" t="n">
-        <v>30.64285714285714</v>
+        <v>28.6</v>
       </c>
       <c r="J14" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="K14" t="n">
+        <v>7</v>
+      </c>
+      <c r="L14" t="n">
         <v>11</v>
       </c>
-      <c r="L14" t="n">
-        <v>17</v>
-      </c>
       <c r="M14" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="N14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O14" t="n">
         <v>1</v>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -4113,16 +4113,16 @@
         <v>12</v>
       </c>
       <c r="B15" t="n">
-        <v>2050.549685408641</v>
+        <v>1927.967132023907</v>
       </c>
       <c r="C15" t="n">
-        <v>146.4678346720458</v>
+        <v>3.526845247748759</v>
       </c>
       <c r="D15" t="n">
-        <v>250.6616883367564</v>
+        <v>2.936599124776175</v>
       </c>
       <c r="E15" t="n">
-        <v>26</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="F15" t="n">
         <v>180.5</v>
@@ -4137,34 +4137,34 @@
         <v>63.64285714285715</v>
       </c>
       <c r="J15" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="K15" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="L15" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="M15" t="n">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="N15" t="n">
         <v>1</v>
       </c>
       <c r="O15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q15" t="n">
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -4172,16 +4172,16 @@
         <v>13</v>
       </c>
       <c r="B16" t="n">
-        <v>2074.113150678282</v>
+        <v>2045.386719215541</v>
       </c>
       <c r="C16" t="n">
-        <v>148.150939334163</v>
+        <v>3.715774960449173</v>
       </c>
       <c r="D16" t="n">
-        <v>246.1580454314868</v>
+        <v>3.046326004766361</v>
       </c>
       <c r="E16" t="n">
-        <v>32.25806451612903</v>
+        <v>45.45454545454545</v>
       </c>
       <c r="F16" t="n">
         <v>129.2142857142857</v>
@@ -4196,34 +4196,34 @@
         <v>23.71428571428572</v>
       </c>
       <c r="J16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K16" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="L16" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="M16" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="N16" t="n">
         <v>1</v>
       </c>
       <c r="O16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P16" t="n">
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -4231,16 +4231,16 @@
         <v>14</v>
       </c>
       <c r="B17" t="n">
-        <v>2376.515944426735</v>
+        <v>2096.306115200388</v>
       </c>
       <c r="C17" t="n">
-        <v>169.7511388876239</v>
+        <v>4.051449460819498</v>
       </c>
       <c r="D17" t="n">
-        <v>291.5478957938131</v>
+        <v>3.439349599420147</v>
       </c>
       <c r="E17" t="n">
-        <v>30.55555555555556</v>
+        <v>52.63157894736842</v>
       </c>
       <c r="F17" t="n">
         <v>63.92857142857143</v>
@@ -4255,22 +4255,22 @@
         <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K17" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="L17" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="M17" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P17" t="n">
         <v>3</v>
@@ -4282,7 +4282,7 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -4290,16 +4290,16 @@
         <v>15</v>
       </c>
       <c r="B18" t="n">
-        <v>2997.050347201556</v>
+        <v>2771.706172501761</v>
       </c>
       <c r="C18" t="n">
-        <v>214.0750248001112</v>
+        <v>5.390639907537794</v>
       </c>
       <c r="D18" t="n">
-        <v>359.488268612976</v>
+        <v>5.085457664821059</v>
       </c>
       <c r="E18" t="n">
-        <v>32.83582089552239</v>
+        <v>51.16279069767442</v>
       </c>
       <c r="F18" t="n">
         <v>94</v>
@@ -4314,22 +4314,22 @@
         <v>88.85714285714286</v>
       </c>
       <c r="J18" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K18" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="L18" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="M18" t="n">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="N18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P18" t="n">
         <v>3</v>
@@ -4338,10 +4338,10 @@
         <v>5</v>
       </c>
       <c r="R18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -4349,16 +4349,16 @@
         <v>16</v>
       </c>
       <c r="B19" t="n">
-        <v>1575.949637276782</v>
+        <v>1473.306840785834</v>
       </c>
       <c r="C19" t="n">
-        <v>112.5678312340559</v>
+        <v>2.86135665024777</v>
       </c>
       <c r="D19" t="n">
-        <v>189.6317750477986</v>
+        <v>2.366814289552878</v>
       </c>
       <c r="E19" t="n">
-        <v>26.31578947368421</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="F19" t="n">
         <v>293.8571428571428</v>
@@ -4376,25 +4376,25 @@
         <v>6</v>
       </c>
       <c r="K19" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L19" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M19" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="N19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R19" t="n">
         <v>2</v>
@@ -4408,16 +4408,16 @@
         <v>17</v>
       </c>
       <c r="B20" t="n">
-        <v>1647.664877646958</v>
+        <v>1522.383240604134</v>
       </c>
       <c r="C20" t="n">
-        <v>117.6903484033541</v>
+        <v>2.699470408271972</v>
       </c>
       <c r="D20" t="n">
-        <v>199.4920160202466</v>
+        <v>2.226607926833399</v>
       </c>
       <c r="E20" t="n">
-        <v>36.8421052631579</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="F20" t="n">
         <v>273.1428571428572</v>
@@ -4432,19 +4432,19 @@
         <v>16.5</v>
       </c>
       <c r="J20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L20" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M20" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O20" t="n">
         <v>2</v>
@@ -4456,10 +4456,10 @@
         <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -4467,16 +4467,16 @@
         <v>18</v>
       </c>
       <c r="B21" t="n">
-        <v>1787.680150921281</v>
+        <v>1748.537459730393</v>
       </c>
       <c r="C21" t="n">
-        <v>127.6914393515201</v>
+        <v>3.16370031958387</v>
       </c>
       <c r="D21" t="n">
-        <v>214.5875103071532</v>
+        <v>2.654007278281674</v>
       </c>
       <c r="E21" t="n">
-        <v>17.30769230769231</v>
+        <v>48</v>
       </c>
       <c r="F21" t="n">
         <v>76.07142857142857</v>
@@ -4491,16 +4491,16 @@
         <v>94.21428571428571</v>
       </c>
       <c r="J21" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="K21" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="L21" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="M21" t="n">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="N21" t="n">
         <v>2</v>
@@ -4509,16 +4509,16 @@
         <v>2</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q21" t="n">
         <v>2</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -4526,16 +4526,16 @@
         <v>19</v>
       </c>
       <c r="B22" t="n">
-        <v>1668.706165887133</v>
+        <v>1400.989608589542</v>
       </c>
       <c r="C22" t="n">
-        <v>119.1932975633666</v>
+        <v>2.886729779838057</v>
       </c>
       <c r="D22" t="n">
-        <v>206.8146785296849</v>
+        <v>2.417166701919104</v>
       </c>
       <c r="E22" t="n">
-        <v>19.23076923076923</v>
+        <v>37.5</v>
       </c>
       <c r="F22" t="n">
         <v>41.28571428571428</v>
@@ -4550,16 +4550,16 @@
         <v>56.42857142857143</v>
       </c>
       <c r="J22" t="n">
+        <v>5</v>
+      </c>
+      <c r="K22" t="n">
+        <v>5</v>
+      </c>
+      <c r="L22" t="n">
         <v>8</v>
       </c>
-      <c r="K22" t="n">
-        <v>7</v>
-      </c>
-      <c r="L22" t="n">
-        <v>13</v>
-      </c>
       <c r="M22" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="N22" t="n">
         <v>2</v>
@@ -4571,7 +4571,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
         <v>3</v>
@@ -4585,16 +4585,16 @@
         <v>20</v>
       </c>
       <c r="B23" t="n">
-        <v>2334.9163886803</v>
+        <v>2422.211408299246</v>
       </c>
       <c r="C23" t="n">
-        <v>166.7797420485929</v>
+        <v>4.044807409760835</v>
       </c>
       <c r="D23" t="n">
-        <v>278.4241677446092</v>
+        <v>3.405652096874545</v>
       </c>
       <c r="E23" t="n">
-        <v>27.11864406779661</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="F23" t="n">
         <v>136.7142857142857</v>
@@ -4609,34 +4609,34 @@
         <v>71.78571428571429</v>
       </c>
       <c r="J23" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="K23" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="L23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M23" t="n">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="N23" t="n">
         <v>3</v>
       </c>
       <c r="O23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R23" t="n">
         <v>2</v>
       </c>
       <c r="S23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -4644,16 +4644,16 @@
         <v>21</v>
       </c>
       <c r="B24" t="n">
-        <v>2305.176781791344</v>
+        <v>1895.473404959655</v>
       </c>
       <c r="C24" t="n">
-        <v>164.6554844136674</v>
+        <v>3.730861698939818</v>
       </c>
       <c r="D24" t="n">
-        <v>286.6266923313281</v>
+        <v>3.001250237858613</v>
       </c>
       <c r="E24" t="n">
-        <v>29.72972972972973</v>
+        <v>37.5</v>
       </c>
       <c r="F24" t="n">
         <v>165.1428571428571</v>
@@ -4668,34 +4668,34 @@
         <v>66.5</v>
       </c>
       <c r="J24" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K24" t="n">
+        <v>7</v>
+      </c>
+      <c r="L24" t="n">
         <v>9</v>
       </c>
-      <c r="L24" t="n">
-        <v>18</v>
-      </c>
       <c r="M24" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="N24" t="n">
         <v>1</v>
       </c>
       <c r="O24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -4703,16 +4703,16 @@
         <v>22</v>
       </c>
       <c r="B25" t="n">
-        <v>2677.512591436551</v>
+        <v>2556.512451165171</v>
       </c>
       <c r="C25" t="n">
-        <v>191.2508993883251</v>
+        <v>4.68816645358689</v>
       </c>
       <c r="D25" t="n">
-        <v>328.8647314081939</v>
+        <v>3.888724549408914</v>
       </c>
       <c r="E25" t="n">
-        <v>31.48148148148148</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="F25" t="n">
         <v>86.85714285714286</v>
@@ -4727,34 +4727,34 @@
         <v>53.07142857142857</v>
       </c>
       <c r="J25" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="K25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L25" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="M25" t="n">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="N25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O25" t="n">
         <v>2</v>
       </c>
       <c r="P25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q25" t="n">
         <v>3</v>
       </c>
       <c r="R25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -4762,16 +4762,16 @@
         <v>23</v>
       </c>
       <c r="B26" t="n">
-        <v>2772.447789426909</v>
+        <v>2344.901139066541</v>
       </c>
       <c r="C26" t="n">
-        <v>198.0319849590649</v>
+        <v>4.597229490871086</v>
       </c>
       <c r="D26" t="n">
-        <v>343.4122200149967</v>
+        <v>4.030228285912738</v>
       </c>
       <c r="E26" t="n">
-        <v>24.07407407407407</v>
+        <v>59.25925925925926</v>
       </c>
       <c r="F26" t="n">
         <v>83</v>
@@ -4786,34 +4786,34 @@
         <v>103.0714285714286</v>
       </c>
       <c r="J26" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K26" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="L26" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="M26" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="N26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P26" t="n">
         <v>2</v>
       </c>
       <c r="Q26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S26" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -4821,16 +4821,16 @@
         <v>24</v>
       </c>
       <c r="B27" t="n">
-        <v>1851.398190151301</v>
+        <v>1788.386223339223</v>
       </c>
       <c r="C27" t="n">
-        <v>132.2427278679501</v>
+        <v>3.346464186343488</v>
       </c>
       <c r="D27" t="n">
-        <v>230.9233266896512</v>
+        <v>3.068391853821484</v>
       </c>
       <c r="E27" t="n">
-        <v>44</v>
+        <v>52.38095238095238</v>
       </c>
       <c r="F27" t="n">
         <v>145.5714285714286</v>
@@ -4851,16 +4851,16 @@
         <v>8</v>
       </c>
       <c r="L27" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="M27" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P27" t="n">
         <v>2</v>
@@ -4880,16 +4880,16 @@
         <v>25</v>
       </c>
       <c r="B28" t="n">
-        <v>1701.488579931803</v>
+        <v>1426.424015070117</v>
       </c>
       <c r="C28" t="n">
-        <v>121.5348985665574</v>
+        <v>2.836803568914488</v>
       </c>
       <c r="D28" t="n">
-        <v>207.064067675188</v>
+        <v>2.316673363660233</v>
       </c>
       <c r="E28" t="n">
-        <v>22.58064516129032</v>
+        <v>40</v>
       </c>
       <c r="F28" t="n">
         <v>178.8571428571429</v>
@@ -4904,22 +4904,22 @@
         <v>97.07142857142857</v>
       </c>
       <c r="J28" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="K28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L28" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="M28" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="N28" t="n">
         <v>1</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P28" t="n">
         <v>2</v>
@@ -4939,46 +4939,46 @@
         <v>26</v>
       </c>
       <c r="B29" t="n">
-        <v>2371.850349710029</v>
+        <v>2238.848221066341</v>
       </c>
       <c r="C29" t="n">
-        <v>169.4178821221449</v>
+        <v>4.097769417612504</v>
       </c>
       <c r="D29" t="n">
-        <v>290.2447311462649</v>
+        <v>3.735088214964795</v>
       </c>
       <c r="E29" t="n">
-        <v>31.81818181818182</v>
+        <v>48.27586206896552</v>
       </c>
       <c r="F29" t="n">
-        <v>118.1428571428571</v>
+        <v>110.2666666666667</v>
       </c>
       <c r="G29" t="n">
-        <v>145.2857142857143</v>
+        <v>135.6</v>
       </c>
       <c r="H29" t="n">
-        <v>81.42857142857143</v>
+        <v>76</v>
       </c>
       <c r="I29" t="n">
-        <v>36.57142857142857</v>
+        <v>34.13333333333333</v>
       </c>
       <c r="J29" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="K29" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L29" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="M29" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="N29" t="n">
         <v>4</v>
       </c>
       <c r="O29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
         <v>2</v>
@@ -4987,7 +4987,7 @@
         <v>3</v>
       </c>
       <c r="R29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -4998,16 +4998,16 @@
         <v>27</v>
       </c>
       <c r="B30" t="n">
-        <v>1634.639726235981</v>
+        <v>1423.082252163248</v>
       </c>
       <c r="C30" t="n">
-        <v>116.7599804454272</v>
+        <v>2.814068722441002</v>
       </c>
       <c r="D30" t="n">
-        <v>200.276188871615</v>
+        <v>2.372018631811201</v>
       </c>
       <c r="E30" t="n">
-        <v>26.92307692307692</v>
+        <v>38.46153846153846</v>
       </c>
       <c r="F30" t="n">
         <v>204.3571428571429</v>
@@ -5022,22 +5022,22 @@
         <v>58.85714285714285</v>
       </c>
       <c r="J30" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K30" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L30" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="M30" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="N30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P30" t="n">
         <v>0</v>
@@ -5046,10 +5046,10 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -5057,16 +5057,16 @@
         <v>28</v>
       </c>
       <c r="B31" t="n">
-        <v>2433.845937784514</v>
+        <v>2732.395262356928</v>
       </c>
       <c r="C31" t="n">
-        <v>173.8461384131796</v>
+        <v>4.301417142191446</v>
       </c>
       <c r="D31" t="n">
-        <v>285.0887030365463</v>
+        <v>3.567592285447175</v>
       </c>
       <c r="E31" t="n">
-        <v>24</v>
+        <v>52.17391304347826</v>
       </c>
       <c r="F31" t="n">
         <v>106.5714285714286</v>
@@ -5081,31 +5081,31 @@
         <v>107.5714285714286</v>
       </c>
       <c r="J31" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="K31" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="L31" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="M31" t="n">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="N31" t="n">
         <v>6</v>
       </c>
       <c r="O31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R31" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -5116,16 +5116,16 @@
         <v>29</v>
       </c>
       <c r="B32" t="n">
-        <v>2226.052442555076</v>
+        <v>2237.341184740749</v>
       </c>
       <c r="C32" t="n">
-        <v>159.0037458967911</v>
+        <v>3.933611768290356</v>
       </c>
       <c r="D32" t="n">
-        <v>268.4476346471055</v>
+        <v>3.533586895945757</v>
       </c>
       <c r="E32" t="n">
-        <v>21.05263157894737</v>
+        <v>38.46153846153846</v>
       </c>
       <c r="F32" t="n">
         <v>117.3571428571429</v>
@@ -5140,19 +5140,19 @@
         <v>54.07142857142857</v>
       </c>
       <c r="J32" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="K32" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L32" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="M32" t="n">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O32" t="n">
         <v>2</v>
@@ -5164,7 +5164,7 @@
         <v>4</v>
       </c>
       <c r="R32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -5175,16 +5175,16 @@
         <v>30</v>
       </c>
       <c r="B33" t="n">
-        <v>2088.575097939589</v>
+        <v>2202.158330489449</v>
       </c>
       <c r="C33" t="n">
-        <v>149.1839355671135</v>
+        <v>3.752354345706378</v>
       </c>
       <c r="D33" t="n">
-        <v>248.938239768764</v>
+        <v>3.140730679842598</v>
       </c>
       <c r="E33" t="n">
-        <v>28</v>
+        <v>58.62068965517241</v>
       </c>
       <c r="F33" t="n">
         <v>145.4285714285714</v>
@@ -5199,34 +5199,34 @@
         <v>37.21428571428572</v>
       </c>
       <c r="J33" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="K33" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L33" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="M33" t="n">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="N33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S33" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34">
@@ -5234,16 +5234,16 @@
         <v>31</v>
       </c>
       <c r="B34" t="n">
-        <v>1344.265635358625</v>
+        <v>1212.246483783053</v>
       </c>
       <c r="C34" t="n">
-        <v>96.01897395418753</v>
+        <v>2.182608503446942</v>
       </c>
       <c r="D34" t="n">
-        <v>161.0734817313497</v>
+        <v>1.794720905073241</v>
       </c>
       <c r="E34" t="n">
-        <v>18.18181818181818</v>
+        <v>28.57142857142857</v>
       </c>
       <c r="F34" t="n">
         <v>243</v>
@@ -5258,16 +5258,16 @@
         <v>61.35714285714285</v>
       </c>
       <c r="J34" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L34" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="M34" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
@@ -5293,16 +5293,16 @@
         <v>32</v>
       </c>
       <c r="B35" t="n">
-        <v>5429.403831493169</v>
+        <v>8131.391980512733</v>
       </c>
       <c r="C35" t="n">
-        <v>387.8145593923692</v>
+        <v>9.756542348055476</v>
       </c>
       <c r="D35" t="n">
-        <v>618.2862681108132</v>
+        <v>7.802901999225409</v>
       </c>
       <c r="E35" t="n">
-        <v>76.51006711409396</v>
+        <v>82.3943661971831</v>
       </c>
       <c r="F35" t="n">
         <v>126.6428571428571</v>
@@ -5320,19 +5320,19 @@
         <v>52</v>
       </c>
       <c r="K35" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L35" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="M35" t="n">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="N35" t="n">
         <v>1</v>
       </c>
       <c r="O35" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="P35" t="n">
         <v>38</v>
@@ -5341,10 +5341,10 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S35" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="36">
@@ -5352,16 +5352,16 @@
         <v>33</v>
       </c>
       <c r="B36" t="n">
-        <v>3358.409209102542</v>
+        <v>3362.589175841802</v>
       </c>
       <c r="C36" t="n">
-        <v>239.886372078753</v>
+        <v>5.794689603517939</v>
       </c>
       <c r="D36" t="n">
-        <v>397.9989420587697</v>
+        <v>5.10495006294669</v>
       </c>
       <c r="E36" t="n">
-        <v>25.55555555555556</v>
+        <v>48.14814814814815</v>
       </c>
       <c r="F36" t="n">
         <v>72.57142857142857</v>
@@ -5376,34 +5376,34 @@
         <v>121.7857142857143</v>
       </c>
       <c r="J36" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="K36" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="L36" t="n">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="M36" t="n">
-        <v>87</v>
+        <v>55</v>
       </c>
       <c r="N36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O36" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="P36" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S36" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37">
@@ -5411,16 +5411,16 @@
         <v>34</v>
       </c>
       <c r="B37" t="n">
-        <v>3121.126323791447</v>
+        <v>3020.40795312378</v>
       </c>
       <c r="C37" t="n">
-        <v>222.9375945565319</v>
+        <v>5.641901212507492</v>
       </c>
       <c r="D37" t="n">
-        <v>382.9004209697931</v>
+        <v>4.703343687464428</v>
       </c>
       <c r="E37" t="n">
-        <v>35.9375</v>
+        <v>62.5</v>
       </c>
       <c r="F37" t="n">
         <v>114.7142857142857</v>
@@ -5435,19 +5435,19 @@
         <v>56.21428571428572</v>
       </c>
       <c r="J37" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="K37" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="L37" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="M37" t="n">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="N37" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5459,10 +5459,10 @@
         <v>6</v>
       </c>
       <c r="R37" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="S37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -5470,16 +5470,16 @@
         <v>35</v>
       </c>
       <c r="B38" t="n">
-        <v>2196.94999849102</v>
+        <v>2199.222109761831</v>
       </c>
       <c r="C38" t="n">
-        <v>156.9249998922157</v>
+        <v>3.929744585777549</v>
       </c>
       <c r="D38" t="n">
-        <v>263.5398725918567</v>
+        <v>3.275836108774536</v>
       </c>
       <c r="E38" t="n">
-        <v>36.11111111111111</v>
+        <v>50</v>
       </c>
       <c r="F38" t="n">
         <v>39.85714285714285</v>
@@ -5494,28 +5494,28 @@
         <v>33.78571428571428</v>
       </c>
       <c r="J38" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K38" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="L38" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M38" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P38" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -5529,16 +5529,16 @@
         <v>36</v>
       </c>
       <c r="B39" t="n">
-        <v>1698.847421009787</v>
+        <v>1569.191968578506</v>
       </c>
       <c r="C39" t="n">
-        <v>121.3462443578419</v>
+        <v>2.911551761507631</v>
       </c>
       <c r="D39" t="n">
-        <v>205.9954432093245</v>
+        <v>2.445625783247733</v>
       </c>
       <c r="E39" t="n">
-        <v>24.13793103448276</v>
+        <v>60</v>
       </c>
       <c r="F39" t="n">
         <v>217.6428571428571</v>
@@ -5553,31 +5553,31 @@
         <v>37.71428571428572</v>
       </c>
       <c r="J39" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="K39" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L39" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="M39" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S39" t="n">
         <v>3</v>
@@ -5588,16 +5588,16 @@
         <v>37</v>
       </c>
       <c r="B40" t="n">
-        <v>3686.518249829113</v>
+        <v>3605.947948291463</v>
       </c>
       <c r="C40" t="n">
-        <v>263.322732130651</v>
+        <v>5.889043978302583</v>
       </c>
       <c r="D40" t="n">
-        <v>448.8849889894494</v>
+        <v>5.557391730552651</v>
       </c>
       <c r="E40" t="n">
-        <v>23.80952380952381</v>
+        <v>55.81395348837209</v>
       </c>
       <c r="F40" t="n">
         <v>171.1428571428571</v>
@@ -5612,34 +5612,34 @@
         <v>30.78571428571428</v>
       </c>
       <c r="J40" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="K40" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="L40" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="M40" t="n">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="N40" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q40" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="R40" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S40" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -5647,16 +5647,16 @@
         <v>38</v>
       </c>
       <c r="B41" t="n">
-        <v>2426.537931327618</v>
+        <v>2149.428029295685</v>
       </c>
       <c r="C41" t="n">
-        <v>173.3241379519727</v>
+        <v>4.166991177196905</v>
       </c>
       <c r="D41" t="n">
-        <v>298.3938772494471</v>
+        <v>3.494145639582964</v>
       </c>
       <c r="E41" t="n">
-        <v>16.12903225806452</v>
+        <v>39.39393939393939</v>
       </c>
       <c r="F41" t="n">
         <v>145.2142857142857</v>
@@ -5671,34 +5671,34 @@
         <v>85.14285714285714</v>
       </c>
       <c r="J41" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K41" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L41" t="n">
+        <v>10</v>
+      </c>
+      <c r="M41" t="n">
         <v>34</v>
       </c>
-      <c r="M41" t="n">
-        <v>62</v>
-      </c>
       <c r="N41" t="n">
         <v>3</v>
       </c>
       <c r="O41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R41" t="n">
         <v>1</v>
       </c>
       <c r="S41" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42">
@@ -5706,16 +5706,16 @@
         <v>39</v>
       </c>
       <c r="B42" t="n">
-        <v>2041.00321258104</v>
+        <v>2098.517053527364</v>
       </c>
       <c r="C42" t="n">
-        <v>145.7859437557885</v>
+        <v>3.534164596238427</v>
       </c>
       <c r="D42" t="n">
-        <v>249.0837095001492</v>
+        <v>3.226711613805077</v>
       </c>
       <c r="E42" t="n">
-        <v>41.66666666666666</v>
+        <v>64.28571428571429</v>
       </c>
       <c r="F42" t="n">
         <v>117.5</v>
@@ -5730,25 +5730,25 @@
         <v>35.21428571428572</v>
       </c>
       <c r="J42" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K42" t="n">
         <v>11</v>
       </c>
       <c r="L42" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="M42" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="N42" t="n">
         <v>3</v>
       </c>
       <c r="O42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q42" t="n">
         <v>1</v>
@@ -5765,16 +5765,16 @@
         <v>40</v>
       </c>
       <c r="B43" t="n">
-        <v>2338.322677378554</v>
+        <v>3087.249919033708</v>
       </c>
       <c r="C43" t="n">
-        <v>167.0230483841824</v>
+        <v>4.22371144881006</v>
       </c>
       <c r="D43" t="n">
-        <v>277.8496885757372</v>
+        <v>3.47454139749179</v>
       </c>
       <c r="E43" t="n">
-        <v>56</v>
+        <v>76.19047619047619</v>
       </c>
       <c r="F43" t="n">
         <v>104.6428571428571</v>
@@ -5789,34 +5789,34 @@
         <v>42.71428571428572</v>
       </c>
       <c r="J43" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K43" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="L43" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="M43" t="n">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P43" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Q43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
         <v>1</v>
       </c>
       <c r="S43" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="44">
@@ -5824,16 +5824,16 @@
         <v>41</v>
       </c>
       <c r="B44" t="n">
-        <v>2748.558159506376</v>
+        <v>2777.043823047374</v>
       </c>
       <c r="C44" t="n">
-        <v>196.325582821884</v>
+        <v>4.890044061987511</v>
       </c>
       <c r="D44" t="n">
-        <v>331.2682973525192</v>
+        <v>3.979312262668035</v>
       </c>
       <c r="E44" t="n">
-        <v>29.62962962962963</v>
+        <v>39.02439024390244</v>
       </c>
       <c r="F44" t="n">
         <v>108.1428571428571</v>
@@ -5848,16 +5848,16 @@
         <v>40.78571428571428</v>
       </c>
       <c r="J44" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K44" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="L44" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="M44" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="N44" t="n">
         <v>3</v>
@@ -5866,16 +5866,16 @@
         <v>2</v>
       </c>
       <c r="P44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q44" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R44" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -5883,16 +5883,16 @@
         <v>42</v>
       </c>
       <c r="B45" t="n">
-        <v>2623.495399048816</v>
+        <v>2619.664615286428</v>
       </c>
       <c r="C45" t="n">
-        <v>187.3925285034869</v>
+        <v>4.652259062126925</v>
       </c>
       <c r="D45" t="n">
-        <v>315.5257968099663</v>
+        <v>3.757212816144812</v>
       </c>
       <c r="E45" t="n">
-        <v>28.57142857142857</v>
+        <v>50</v>
       </c>
       <c r="F45" t="n">
         <v>155</v>
@@ -5907,34 +5907,34 @@
         <v>24.5</v>
       </c>
       <c r="J45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K45" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="L45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="M45" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="N45" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P45" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q45" t="n">
         <v>3</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -5942,16 +5942,16 @@
         <v>43</v>
       </c>
       <c r="B46" t="n">
-        <v>2421.934139733232</v>
+        <v>2123.077941610966</v>
       </c>
       <c r="C46" t="n">
-        <v>172.9952956952309</v>
+        <v>4.201626089710222</v>
       </c>
       <c r="D46" t="n">
-        <v>291.1824038710812</v>
+        <v>3.262303661534347</v>
       </c>
       <c r="E46" t="n">
-        <v>33.33333333333334</v>
+        <v>47.05882352941177</v>
       </c>
       <c r="F46" t="n">
         <v>50.07142857142857</v>
@@ -5966,19 +5966,19 @@
         <v>9.071428571428571</v>
       </c>
       <c r="J46" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K46" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L46" t="n">
         <v>7</v>
       </c>
       <c r="M46" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="N46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O46" t="n">
         <v>1</v>
@@ -5990,7 +5990,7 @@
         <v>3</v>
       </c>
       <c r="R46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S46" t="n">
         <v>1</v>
